--- a/docs/downloads/Oshawa.xlsx
+++ b/docs/downloads/Oshawa.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D836"/>
+  <dimension ref="A1:D834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17235,17 +17235,17 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Elvis</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Sequeira</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>roshini.sequeira@gmail.com</t>
+          <t>elvispeter.lewis@gmail.com</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -17257,19 +17257,15 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>Arnold</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Lewis</t>
-        </is>
-      </c>
-      <c r="C818" t="inlineStr">
-        <is>
-          <t>arnoldelewis@gmail.com</t>
-        </is>
-      </c>
+          <t>Abkarian</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17279,19 +17275,15 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>Elvis</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Lewis</t>
-        </is>
-      </c>
-      <c r="C819" t="inlineStr">
-        <is>
-          <t>elvispeter.lewis@gmail.com</t>
-        </is>
-      </c>
+          <t>Abkarian</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17301,12 +17293,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Abkarian</t>
+          <t>davidson 1</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
@@ -17319,12 +17311,12 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Abkarian</t>
+          <t>Amenta</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -17337,12 +17329,12 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>davidson 1</t>
+          <t>Amenta</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
@@ -17355,12 +17347,12 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Amenta</t>
+          <t>Mapalo</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -17373,12 +17365,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Amenta</t>
+          <t>Arnett</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
@@ -17391,12 +17383,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Mapalo</t>
+          <t>Stefik</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
@@ -17409,12 +17401,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Arnett</t>
+          <t>Langille</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
@@ -17427,15 +17419,19 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Nineesha</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Stefik</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr"/>
+          <t>Nigli</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>nineeshal@gmail.com</t>
+        </is>
+      </c>
       <c r="D827" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17445,15 +17441,19 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Langille</t>
-        </is>
-      </c>
-      <c r="C828" t="inlineStr"/>
+          <t>Betteridge</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>wendy.betteridge@telus.com</t>
+        </is>
+      </c>
       <c r="D828" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17463,17 +17463,17 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>Nineesha</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Nigli</t>
+          <t>Fox</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>nineeshal@gmail.com</t>
+          <t>virginia.foxbrear@gmail.com</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -17485,19 +17485,15 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Betteridge</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>wendy.betteridge@telus.com</t>
-        </is>
-      </c>
+          <t>Osorio</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17507,19 +17503,15 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Philip Jordan</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Fox</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr">
-        <is>
-          <t>virginia.foxbrear@gmail.com</t>
-        </is>
-      </c>
+          <t>Osorio</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -17529,12 +17521,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Osorio</t>
+          <t>Orr</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -17547,12 +17539,12 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>Philip Jordan</t>
+          <t>Kayleigh</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Osorio</t>
+          <t>DonPaul</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -17575,42 +17567,6 @@
       </c>
       <c r="C834" t="inlineStr"/>
       <c r="D834" t="inlineStr">
-        <is>
-          <t>oshawa@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>Kayleigh</t>
-        </is>
-      </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>DonPaul</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr"/>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>oshawa@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>Orr</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr"/>
-      <c r="D836" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Oshawa.xlsx
+++ b/docs/downloads/Oshawa.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D947"/>
+  <dimension ref="A1:D954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Abhijayendra</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Coughlan</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>owencogster@gmail.com</t>
+          <t>aha_neo@yahoo.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marg</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reeve</t>
+          <t>Coughlan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>reeve.marg@gmail.com</t>
+          <t>owencogster@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Marg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Galea</t>
+          <t>Reeve</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>spacecaps24@outlook.com</t>
+          <t>reeve.marg@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Huntington</t>
+          <t>Galea</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>carol_l_huntington@yahoo.ca</t>
+          <t>spacecaps24@outlook.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fegan</t>
+          <t>Huntington</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pafegan@sympatico.ca</t>
+          <t>carol_l_huntington@yahoo.ca</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Fegan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>marye.luna@gmail.com</t>
+          <t>pafegan@sympatico.ca</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cindysomerville7@gmail.com</t>
+          <t>marye.luna@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cameron</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ryandcameron82@gmail.com</t>
+          <t>cindysomerville7@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Barron</t>
+          <t>Cameron</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>billbarron@gmail.com</t>
+          <t>ryandcameron82@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Barron</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>chad.brooks@prenelove.com</t>
+          <t>billbarron@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Louis</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Landry</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>loumar.landry5@gmail.com</t>
+          <t>chad.brooks@prenelove.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Em</t>
+          <t>Louis</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Landry</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>amtbeaton@gmail.com</t>
+          <t>loumar.landry5@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Em</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Spooner</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>yahanspooner1@gmail.com</t>
+          <t>amtbeaton@gmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Spooner</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jacob.g.garcia@outlook.com</t>
+          <t>yahanspooner1@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Van luven</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>don.vanluven@gmail.com</t>
+          <t>jacob.g.garcia@outlook.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kecman</t>
+          <t>Van luven</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>74subscribe@gmail.com</t>
+          <t>don.vanluven@gmail.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Luciano</t>
+          <t>Kecman</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>babs5203@aol.com</t>
+          <t>74subscribe@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Labar</t>
+          <t>Luciano</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>timlabar@hotmail.com</t>
+          <t>babs5203@aol.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Deanna</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Haarlem</t>
+          <t>Labar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dhaarlem@hotmail.ca</t>
+          <t>timlabar@hotmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Deanna</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Haarlem</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>robert.palmer@asylumresource.com</t>
+          <t>dhaarlem@hotmail.ca</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Schisler</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>lori.schisler@hotmail.com</t>
+          <t>robert.palmer@asylumresource.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Traer-dickson</t>
+          <t>Schisler</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>janet.traer@gmail.com</t>
+          <t>lori.schisler@hotmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Janet</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sampath-persaud</t>
+          <t>Traer-dickson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mel.sam29@hotmail.com</t>
+          <t>janet.traer@gmail.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Sampath-persaud</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kyle_mohammed@yahoo.com</t>
+          <t>mel.sam29@hotmail.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Astrop</t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>simonastrop@icloud.com</t>
+          <t>kyle_mohammed@yahoo.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Astrop</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>maria.a.cortes92@gmail.com</t>
+          <t>simonastrop@icloud.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jahope1013@outlook.com</t>
+          <t>maria.a.cortes92@gmail.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Conlon</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>conlon.chris@gmail.com</t>
+          <t>jahope1013@outlook.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Opara</t>
+          <t>Conlon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>robertopara001@gmail.com</t>
+          <t>conlon.chris@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Anam</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Israr</t>
+          <t>Opara</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>asiaisrar77@gmail.com</t>
+          <t>robertopara001@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jill</t>
+          <t>Anam</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shepperd</t>
+          <t>Israr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jillshepperd1954@gmail.com</t>
+          <t>asiaisrar77@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Jill</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Shepperd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>adam.jpscott@gmail.com</t>
+          <t>jillshepperd1954@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Flynn</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>marionrose.flynn@gmail.com</t>
+          <t>adam.jpscott@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Janssen</t>
+          <t>Flynn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>hannahjanssen1998@gmail.com</t>
+          <t>marionrose.flynn@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Casimirio</t>
+          <t>Janssen</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>casimiriom70@live.com</t>
+          <t>hannahjanssen1998@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,17 +2349,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Casimirio</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>johnston1976@gmail.com</t>
+          <t>casimiriom70@live.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2371,17 +2371,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nye</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>lisanye@gmail.com</t>
+          <t>johnston1976@gmail.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2393,17 +2393,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lex</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Luther</t>
+          <t>Nye</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>e5lex.e5@gmail.com</t>
+          <t>lisanye@gmail.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Lex</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Whittall</t>
+          <t>Luther</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>kristenwhittall@gmail.com</t>
+          <t>e5lex.e5@gmail.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2437,17 +2437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scullion</t>
+          <t>Whittall</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>pscullion17@gmail.com</t>
+          <t>kristenwhittall@gmail.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2459,17 +2459,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Scullion</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>crystalrose543@gmail.com</t>
+          <t>pscullion17@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2481,17 +2481,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Geena</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>geena986n@gmail.com</t>
+          <t>crystalrose543@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2503,17 +2503,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Shelley</t>
+          <t>Geena</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bertrim</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>shelley.bertrim@sympatico.ca</t>
+          <t>geena986n@gmail.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2525,17 +2525,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Shelley</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Di felice</t>
+          <t>Bertrim</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>682fern@gmail.com</t>
+          <t>shelley.bertrim@sympatico.ca</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2547,17 +2547,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Maxiine</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Di felice</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>maxineedison@gmail.com</t>
+          <t>682fern@gmail.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2569,17 +2569,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Maxiine</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>haphantom@gmail.com</t>
+          <t>maxineedison@gmail.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2591,17 +2591,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sandyrowny@hotmail.com</t>
+          <t>haphantom@gmail.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2613,17 +2613,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cam</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lowe</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>camoftr@gmail.com</t>
+          <t>sandyrowny@hotmail.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2635,17 +2635,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Gord</t>
+          <t>Cam</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Geissberger</t>
+          <t>Lowe</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ggeissberger@gmail.com</t>
+          <t>camoftr@gmail.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2657,17 +2657,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Randi</t>
+          <t>Gord</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Geissberger</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>randikostka@gmail.com</t>
+          <t>ggeissberger@gmail.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2679,17 +2679,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Randi</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hicks</t>
+          <t>Armstrong</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>littlehicksy@yahoo.ca</t>
+          <t>randikostka@gmail.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2701,17 +2701,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fregonese</t>
+          <t>Hicks</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>alisonfregonese@rogers.com</t>
+          <t>littlehicksy@yahoo.ca</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2723,17 +2723,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Vamsi</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Boyalla</t>
+          <t>Fregonese</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>vamsikrishnaboyalla@gmail.com</t>
+          <t>alisonfregonese@rogers.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2745,17 +2745,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Vamsi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Boyalla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>kylecruz@gmail.com</t>
+          <t>vamsikrishnaboyalla@gmail.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -18781,17 +18781,17 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Tamu</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Guiam  (MPG SPORTS CO.)</t>
+          <t>Bracken</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>mark.p.guiam@mpgsportsco.com</t>
+          <t>tmkbracken@gmail.com</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -18803,15 +18803,19 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>Janos</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Ratonyi</t>
-        </is>
-      </c>
-      <c r="C895" t="inlineStr"/>
+          <t>Guiam  (MPG SPORTS CO.)</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>mark.p.guiam@mpgsportsco.com</t>
+        </is>
+      </c>
       <c r="D895" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -18821,19 +18825,15 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Janos</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Balling</t>
-        </is>
-      </c>
-      <c r="C896" t="inlineStr">
-        <is>
-          <t>fballing64@gmail.com</t>
-        </is>
-      </c>
+          <t>Ratonyi</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr"/>
       <c r="D896" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -18843,17 +18843,17 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>Jolene</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Waese</t>
+          <t>Balling</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>jolene@rogers.com</t>
+          <t>fballing64@gmail.com</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -18865,17 +18865,17 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Jolene</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Hoskin</t>
+          <t>Waese</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>barbhoskin@rogers.com</t>
+          <t>jolene@rogers.com</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -18887,17 +18887,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Weaver</t>
+          <t>Hoskin</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>cathykbawden@gmai.com</t>
+          <t>barbhoskin@rogers.com</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -18909,17 +18909,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>Wayne</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Singer</t>
+          <t>Weaver</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>wayne_singer@yahoo.ca</t>
+          <t>cathykbawden@gmai.com</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -18931,17 +18931,17 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Gladman</t>
+          <t>Singer</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>cindygladmanxo@gmail.com</t>
+          <t>wayne_singer@yahoo.ca</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -18953,17 +18953,17 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>Kelsey</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Gladman</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>kelsey.j.b.taylor@gmail.com</t>
+          <t>cindygladmanxo@gmail.com</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -18975,17 +18975,17 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>wayne</t>
+          <t>Kelsey</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Warburton</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>wayne.binky@gmail.com</t>
+          <t>kelsey.j.b.taylor@gmail.com</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -18997,17 +18997,17 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Reece</t>
+          <t>wayne</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Pritchard</t>
+          <t>Warburton</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>r.scottpritchard@gmail.com</t>
+          <t>wayne.binky@gmail.com</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -19019,17 +19019,17 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Reece</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Pritchard</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>brianyoung1974@gmail.com</t>
+          <t>r.scottpritchard@gmail.com</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -19041,17 +19041,17 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>rachel_meyer5320@hotmail.com</t>
+          <t>brianyoung1974@gmail.com</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
@@ -19063,17 +19063,17 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Qian</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>qyan412@gmail.com</t>
+          <t>rachel_meyer5320@hotmail.com</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -19085,17 +19085,17 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Goselon</t>
+          <t>Qian</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>joshgoselin@gmail.com</t>
+          <t>qyan412@gmail.com</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -19107,17 +19107,17 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>Sébastien</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>OUELLET   DIZON</t>
+          <t>Goselon</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>souellet.dizon@gmail.com</t>
+          <t>joshgoselin@gmail.com</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -19129,17 +19129,17 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Sébastien</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Mian Yin</t>
+          <t>OUELLET   DIZON</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>samanthaminayin@gmail.com</t>
+          <t>souellet.dizon@gmail.com</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
@@ -19151,17 +19151,17 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>Yura</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Yugan</t>
+          <t>Mian Yin</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>yura@gmail.com</t>
+          <t>samanthaminayin@gmail.com</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -19173,17 +19173,17 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Yura</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Nwamma</t>
+          <t>Yugan</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>onuoha.nwamma@gmail.com</t>
+          <t>yura@gmail.com</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -19195,17 +19195,17 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Nieboss</t>
+          <t>Nwamma</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>prince@gmail.ca</t>
+          <t>onuoha.nwamma@gmail.com</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -19217,17 +19217,17 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Prince</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Morash</t>
+          <t>Nieboss</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>c-michellem@hitmail.com</t>
+          <t>prince@gmail.ca</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -19239,17 +19239,17 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>Hoskin</t>
+          <t>Morash</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>kevin_hoskin@outlook.com</t>
+          <t>c-michellem@hitmail.com</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -19261,17 +19261,17 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>Robert Craig</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>Butterworth</t>
+          <t>Hoskin</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>craigscrapyard@gmail.com</t>
+          <t>kevin_hoskin@outlook.com</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -19283,17 +19283,17 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Tima</t>
+          <t>Robert Craig</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>H.</t>
+          <t>Butterworth</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>fatima.alhakimi93@gmail.com</t>
+          <t>craigscrapyard@gmail.com</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -19305,17 +19305,17 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Ida Bagus Puta Puta</t>
+          <t>Tima</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Asana Wibawa</t>
+          <t>H.</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>ida@gmail.com</t>
+          <t>fatima.alhakimi93@gmail.com</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -19327,17 +19327,17 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Mittal</t>
+          <t>Ida Bagus Puta Puta</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Chande</t>
+          <t>Asana Wibawa</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>mittalchande2016@gmail.com</t>
+          <t>ida@gmail.com</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -19349,17 +19349,17 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Mittal</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Jermyn</t>
+          <t>Chande</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>kelvin.j.jermyn@gmail.com</t>
+          <t>mittalchande2016@gmail.com</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -19371,17 +19371,17 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Nicolson</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Jermyn</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>nickxmas47@icloud.com</t>
+          <t>kelvin.j.jermyn@gmail.com</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -19393,17 +19393,17 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Chantal</t>
+          <t>Nicolson</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Boulet</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>chantalboulet07@hotmail.com</t>
+          <t>nickxmas47@icloud.com</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -19415,17 +19415,17 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Chantal</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Morash</t>
+          <t>Boulet</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>c-michellem@hotmail.com</t>
+          <t>chantalboulet07@hotmail.com</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -19437,17 +19437,17 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Evette</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Morash</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>sirillas5@gmail.com</t>
+          <t>c-michellem@hotmail.com</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -19459,17 +19459,17 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Kerie</t>
+          <t>Evette</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>kerie.lynn@yahoo.ca</t>
+          <t>sirillas5@gmail.com</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
@@ -19481,17 +19481,17 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Jill</t>
+          <t>Kerie</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Artates</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>jill.artates8@gmail.com</t>
+          <t>kerie.lynn@yahoo.ca</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
@@ -19503,17 +19503,17 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>Jenna</t>
+          <t>Jill</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Dory</t>
+          <t>Artates</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>jennakdory@gmail.com</t>
+          <t>jill.artates8@gmail.com</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -19525,17 +19525,17 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Jilliane</t>
+          <t>Jenna</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>De La Cruz</t>
+          <t>Dory</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>jillianeclarencedelacruz@gmail.com</t>
+          <t>jennakdory@gmail.com</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -19547,17 +19547,17 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Jilliane</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Osmond</t>
+          <t>De La Cruz</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>brandonosmond@live.ca</t>
+          <t>jillianeclarencedelacruz@gmail.com</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
@@ -19569,17 +19569,17 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Deborah</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Proctor</t>
+          <t>Osmond</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>deborah.proctor27@gmail.com</t>
+          <t>brandonosmond@live.ca</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
@@ -19591,17 +19591,17 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Deborah</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Dolson</t>
+          <t>Proctor</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>sarahdolson55@gmail.com</t>
+          <t>deborah.proctor27@gmail.com</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
@@ -19613,17 +19613,17 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Serena</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>San Cartier</t>
+          <t>Dolson</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>serenasancartier@gmail.com</t>
+          <t>sarahdolson55@gmail.com</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -19635,17 +19635,17 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Serena</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Schroeder</t>
+          <t>San Cartier</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>paul.schroeder29@gmail.com</t>
+          <t>serenasancartier@gmail.com</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
@@ -19662,12 +19662,12 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Schroeder</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>orangepaul17@gmail.com</t>
+          <t>paul.schroeder29@gmail.com</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -19679,17 +19679,17 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Rochelle</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Rock</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>rochelly.tr96@hotmail.com</t>
+          <t>orangepaul17@gmail.com</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -19701,17 +19701,17 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Rochelle</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rock</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>14vivienlynn@gmail.com</t>
+          <t>rochelly.tr96@hotmail.com</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -19723,17 +19723,17 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Gladman</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>maria@gladman.ca</t>
+          <t>14vivienlynn@gmail.com</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -19745,17 +19745,17 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>wayne</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>warburton</t>
+          <t>Gladman</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>wayne.binky@yahoo.com</t>
+          <t>maria@gladman.ca</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -19767,15 +19767,19 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>wayne</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Gladman</t>
-        </is>
-      </c>
-      <c r="C939" t="inlineStr"/>
+          <t>warburton</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>wayne.binky@yahoo.com</t>
+        </is>
+      </c>
       <c r="D939" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -19785,12 +19789,12 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>Gladman</t>
         </is>
       </c>
       <c r="C940" t="inlineStr"/>
@@ -19803,19 +19807,15 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Steele</t>
-        </is>
-      </c>
-      <c r="C941" t="inlineStr">
-        <is>
-          <t>benjaminsteele24@gmail.com</t>
-        </is>
-      </c>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr"/>
       <c r="D941" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -19825,17 +19825,17 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Gladman</t>
+          <t>Steele</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>cindy@gladman.ca</t>
+          <t>benjaminsteele24@gmail.com</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -19847,17 +19847,17 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Calon</t>
+          <t>Gladman</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>vincentdondrey4@gmail.com</t>
+          <t>cindy@gladman.ca</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -19869,17 +19869,17 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Roy</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Simard</t>
+          <t>Calon</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>edwardsimard1960@gmail.com</t>
+          <t>vincentdondrey4@gmail.com</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -19891,17 +19891,17 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Roy</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Reilly</t>
+          <t>Simard</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>contactalexandrareilly@gmail.com</t>
+          <t>edwardsimard1960@gmail.com</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -19913,15 +19913,19 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Gladman</t>
-        </is>
-      </c>
-      <c r="C946" t="inlineStr"/>
+          <t>Reilly</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>contactalexandrareilly@gmail.com</t>
+        </is>
+      </c>
       <c r="D946" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
@@ -19931,20 +19935,166 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
+          <t>Cindy</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Gladman</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr"/>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
           <t>Steve</t>
         </is>
       </c>
-      <c r="B947" t="inlineStr">
+      <c r="B948" t="inlineStr">
         <is>
           <t>Kirkby</t>
         </is>
       </c>
-      <c r="C947" t="inlineStr">
+      <c r="C948" t="inlineStr">
         <is>
           <t>steven.g.kirkby@gmail.com</t>
         </is>
       </c>
-      <c r="D947" t="inlineStr">
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>william.jones@durham.ca</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>huang</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>nancyhmortgage@gmail.com</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Teri</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>chong</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>terijessicachong@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Gillian</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Crosbie</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>gillbritton@gmail.com</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Redden</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr"/>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>oshawa@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Jasper</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Jalandoni</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>jalandoni_ics@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
         <is>
           <t>oshawa@pickleplex.ca</t>
         </is>
